--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.92834309703599</v>
+        <v>2.263355753268348</v>
       </c>
       <c r="D2" t="n">
-        <v>14.55095825541566</v>
+        <v>2.364530716505045</v>
       </c>
       <c r="E2" t="n">
-        <v>10.98740627451199</v>
+        <v>1.785453519608199</v>
       </c>
       <c r="F2" t="n">
-        <v>22.45583436454778</v>
+        <v>3.649073084239014</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.68583085261469</v>
+        <v>3.198947513549887</v>
       </c>
       <c r="D3" t="n">
-        <v>47.91344197666308</v>
+        <v>7.78593432120775</v>
       </c>
       <c r="E3" t="n">
-        <v>10.98740627451199</v>
+        <v>1.785453519608199</v>
       </c>
       <c r="F3" t="n">
-        <v>22.45583436454778</v>
+        <v>3.649073084239014</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.47743647006725</v>
+        <v>6.740083426385928</v>
       </c>
       <c r="D4" t="n">
-        <v>77.3047684672992</v>
+        <v>12.56202487593612</v>
       </c>
       <c r="E4" t="n">
-        <v>10.98740627451199</v>
+        <v>1.785453519608199</v>
       </c>
       <c r="F4" t="n">
-        <v>22.45583436454778</v>
+        <v>3.649073084239014</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.01699262447507</v>
+        <v>5.5277613014772</v>
       </c>
       <c r="D5" t="n">
-        <v>38.80860972443742</v>
+        <v>6.306399080221082</v>
       </c>
       <c r="E5" t="n">
-        <v>10.98740627451199</v>
+        <v>1.785453519608199</v>
       </c>
       <c r="F5" t="n">
-        <v>22.45583436454778</v>
+        <v>3.649073084239014</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
